--- a/data/trans_dic/P42C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P42C_R-Provincia-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -516,39 +516,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya última consulta ginecológica fue en un centro privado</t>
+          <t>Población cuya última consulta ginecológica fue en un centro privado (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -579,21 +569,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -608,9 +583,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -625,17 +597,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,21 +621,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>21,43%</t>
         </is>
@@ -678,47 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,81; 29,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,4; 28,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,34; 26,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,35; 29,15</t>
+          <t>17,81; 29,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,92; 28,64</t>
+          <t>17,4; 28,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,88; 28,01</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,35; 29,15</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16,92; 28,64</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16,88; 28,01</t>
+          <t>16,34; 26,99</t>
         </is>
       </c>
     </row>
@@ -735,17 +677,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,21 +701,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>22,64%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>27,23%</t>
         </is>
@@ -788,47 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,75; 27,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,6; 18,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,14; 31,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,87; 27,17</t>
+          <t>18,75; 27,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,58; 18,72</t>
+          <t>11,6; 18,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,06; 32,36</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,87; 27,17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11,58; 18,72</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>23,06; 32,36</t>
+          <t>23,14; 31,95</t>
         </is>
       </c>
     </row>
@@ -845,17 +757,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,21 +781,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>17,26%</t>
         </is>
@@ -898,47 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,62; 27,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,5; 9,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,08; 21,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,35; 26,36</t>
+          <t>16,62; 27,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,55</t>
+          <t>3,5; 9,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,11; 22,87</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>16,35; 26,36</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3,23; 8,55</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>13,11; 22,87</t>
+          <t>13,08; 21,71</t>
         </is>
       </c>
     </row>
@@ -955,17 +837,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,21 +861,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13,33%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>16,02%</t>
         </is>
@@ -1008,47 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,27; 36,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,37; 17,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,53; 23,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,47; 35,5</t>
+          <t>25,27; 36,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 18,69</t>
+          <t>9,37; 17,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 23,51</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>24,47; 35,5</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9,48; 18,69</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8,08; 23,51</t>
+          <t>7,53; 23,44</t>
         </is>
       </c>
     </row>
@@ -1065,17 +917,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1089,21 +941,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>18,84%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>29,18%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>18,84%</t>
         </is>
@@ -1118,47 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,74; 37,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,57; 7,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,58; 23,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,07; 36,02</t>
+          <t>22,74; 37,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,28</t>
+          <t>1,57; 7,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,5; 24,35</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,07; 36,02</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1,56; 7,28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14,5; 24,35</t>
+          <t>14,58; 23,98</t>
         </is>
       </c>
     </row>
@@ -1175,17 +997,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1199,21 +1021,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>18,0%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>15,79%</t>
         </is>
@@ -1228,47 +1035,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,43; 27,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,03; 24,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,24; 21,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,29; 26,98</t>
+          <t>15,43; 27,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,29; 24,03</t>
+          <t>13,03; 24,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,4; 20,99</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>15,29; 26,98</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>13,29; 24,03</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>11,4; 20,99</t>
+          <t>11,24; 21,6</t>
         </is>
       </c>
     </row>
@@ -1285,17 +1077,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1309,21 +1101,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>45,15%</t>
         </is>
@@ -1338,47 +1115,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,51; 28,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,1; 27,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,58; 49,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,67; 28,39</t>
+          <t>20,51; 28,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,03; 27,26</t>
+          <t>20,1; 27,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,93; 49,63</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20,67; 28,39</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>20,03; 27,26</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>40,93; 49,63</t>
+          <t>40,58; 49,4</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1157,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1419,21 +1181,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>11,52%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,57%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>14,17%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>11,52%</t>
         </is>
@@ -1448,47 +1195,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,06; 26,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,65; 17,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,22; 14,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,11; 26,22</t>
+          <t>19,06; 26,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,32; 17,23</t>
+          <t>11,65; 17,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,76; 14,45</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>19,11; 26,22</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11,32; 17,23</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>8,76; 14,45</t>
+          <t>9,22; 14,75</t>
         </is>
       </c>
     </row>
@@ -1505,17 +1237,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1529,21 +1261,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>23,2%</t>
         </is>
@@ -1558,47 +1275,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,97; 25,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,06; 16,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,01; 25,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22,3; 25,73</t>
+          <t>21,97; 25,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,25; 17,01</t>
+          <t>14,06; 16,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,44; 25,25</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>22,3; 25,73</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>14,25; 17,01</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>20,44; 25,25</t>
+          <t>20,01; 25,0</t>
         </is>
       </c>
     </row>
@@ -1610,13 +1312,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A17"/>
@@ -1635,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1646,39 +1347,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya última consulta ginecológica fue en un centro privado</t>
+          <t>Población cuya última consulta ginecológica fue en un centro privado (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1709,21 +1400,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1738,9 +1414,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1755,17 +1428,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1779,21 +1452,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
@@ -1808,17 +1466,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53670</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50722</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1832,21 +1490,6 @@
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33720</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>53670</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>50722</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>33720</t>
         </is>
@@ -1861,47 +1504,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41826; 69001</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39600; 64124</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25710; 42462</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40760; 68463</t>
+          <t>41826; 69001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38500; 65181</t>
+          <t>39600; 64124</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26559; 44066</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>40760; 68463</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38500; 65181</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>26559; 44066</t>
+          <t>25710; 42462</t>
         </is>
       </c>
     </row>
@@ -1918,17 +1546,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1942,21 +1570,6 @@
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>119</t>
         </is>
@@ -1971,17 +1584,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98357</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59504</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1995,21 +1608,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90181</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98357</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>59504</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>90181</t>
         </is>
@@ -2024,47 +1622,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81457; 118982</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46325; 74109</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>76626; 105832</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81958; 118016</t>
+          <t>81457; 118982</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46274; 74778</t>
+          <t>46325; 74109</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76382; 107171</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>81958; 118016</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>46274; 74778</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>76382; 107171</t>
+          <t>76626; 105832</t>
         </is>
       </c>
     </row>
@@ -2081,17 +1664,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2105,21 +1688,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -2134,17 +1702,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57655</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2158,21 +1726,6 @@
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31000</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>57655</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>15350</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>31000</t>
         </is>
@@ -2187,47 +1740,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44516; 72459</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9661; 25551</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23480; 38981</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43775; 70586</t>
+          <t>44516; 72459</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8900; 23578</t>
+          <t>9661; 25551</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23537; 41075</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>43775; 70586</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8900; 23578</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23537; 41075</t>
+          <t>23480; 38981</t>
         </is>
       </c>
     </row>
@@ -2244,17 +1782,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2268,21 +1806,6 @@
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>86</t>
         </is>
@@ -2297,17 +1820,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86922</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2321,21 +1844,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>52276</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86922</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38040</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>52276</t>
         </is>
@@ -2350,47 +1858,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>72984; 104369</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26729; 50670</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24566; 76512</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>70688; 102537</t>
+          <t>72984; 104369</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27054; 53349</t>
+          <t>26729; 50670</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26385; 76728</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>70688; 102537</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>27054; 53349</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>26385; 76728</t>
+          <t>24566; 76512</t>
         </is>
       </c>
     </row>
@@ -2407,17 +1900,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2431,21 +1924,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
@@ -2460,17 +1938,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49433</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24352</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2484,21 +1962,6 @@
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24352</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>49433</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>6221</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>24352</t>
         </is>
@@ -2513,47 +1976,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38527; 63361</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2659; 12478</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18848; 30994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37386; 61010</t>
+          <t>38527; 63361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2633; 12313</t>
+          <t>2659; 12478</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18737; 31469</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>37386; 61010</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2633; 12313</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>18737; 31469</t>
+          <t>18848; 30994</t>
         </is>
       </c>
     </row>
@@ -2570,17 +2018,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2594,21 +2042,6 @@
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -2623,17 +2056,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44953</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37313</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2647,21 +2080,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>21625</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>44953</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>37313</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>21625</t>
         </is>
@@ -2676,47 +2094,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33142; 59283</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27003; 50069</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15391; 29575</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32832; 57945</t>
+          <t>33142; 59283</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27545; 49804</t>
+          <t>27003; 50069</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15614; 28742</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>32832; 57945</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>27545; 49804</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>15614; 28742</t>
+          <t>15391; 29575</t>
         </is>
       </c>
     </row>
@@ -2733,17 +2136,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>246</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2757,21 +2160,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>246</t>
         </is>
@@ -2786,17 +2174,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135901</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>127274</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170898</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2810,21 +2198,6 @@
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>170898</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>135901</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>127274</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>170898</t>
         </is>
@@ -2839,47 +2212,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>114717; 157733</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>108772; 148909</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>153629; 187004</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>115629; 158821</t>
+          <t>114717; 157733</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>108366; 147521</t>
+          <t>108772; 148909</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>154924; 187866</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>115629; 158821</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>108366; 147521</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>154924; 187866</t>
+          <t>153629; 187004</t>
         </is>
       </c>
     </row>
@@ -2896,17 +2254,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2920,21 +2278,6 @@
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
@@ -2949,17 +2292,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>128784</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95108</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43286</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2973,21 +2316,6 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>43286</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>128784</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>95108</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>43286</t>
         </is>
@@ -3002,47 +2330,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>108737; 150557</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>78186; 117650</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34633; 55403</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>109014; 149600</t>
+          <t>108737; 150557</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>75924; 115638</t>
+          <t>78186; 117650</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32910; 54286</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>109014; 149600</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>75924; 115638</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>32910; 54286</t>
+          <t>34633; 55403</t>
         </is>
       </c>
     </row>
@@ -3059,17 +2372,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>404</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3083,21 +2396,6 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>711</t>
         </is>
@@ -3112,17 +2410,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>655675</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429531</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>467337</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3136,21 +2434,6 @@
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>467337</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>655675</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>429531</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>467337</t>
         </is>
@@ -3165,47 +2448,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>601929; 701351</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>390425; 470981</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>403168; 503641</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>611083; 705108</t>
+          <t>601929; 701351</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>395628; 472258</t>
+          <t>390425; 470981</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>411727; 508802</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>611083; 705108</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>395628; 472258</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>411727; 508802</t>
+          <t>403168; 503641</t>
         </is>
       </c>
     </row>
@@ -3217,7 +2485,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3225,9 +2493,8 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A25:A27"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A28:A30"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A28:A30"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>

--- a/data/trans_dic/P42C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P42C_R-Provincia-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,81; 29,38</t>
+          <t>17,47; 29,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,4; 28,18</t>
+          <t>16,84; 28,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 26,99</t>
+          <t>14,88; 24,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,81; 29,38</t>
+          <t>17,47; 29,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,4; 28,18</t>
+          <t>16,84; 28,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 26,99</t>
+          <t>14,88; 24,18</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,75; 27,39</t>
+          <t>18,44; 26,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,6; 18,55</t>
+          <t>11,58; 18,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,14; 31,95</t>
+          <t>23,28; 32,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,75; 27,39</t>
+          <t>18,44; 26,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,6; 18,55</t>
+          <t>11,58; 18,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,14; 31,95</t>
+          <t>23,28; 32,17</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,62; 27,06</t>
+          <t>16,71; 27,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,27</t>
+          <t>3,33; 8,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,08; 21,71</t>
+          <t>12,49; 21,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,62; 27,06</t>
+          <t>16,71; 27,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,27</t>
+          <t>3,33; 8,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,08; 21,71</t>
+          <t>12,49; 21,32</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,27; 36,13</t>
+          <t>25,2; 35,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 17,76</t>
+          <t>9,35; 18,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 23,44</t>
+          <t>19,35; 28,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,27; 36,13</t>
+          <t>25,2; 35,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 17,76</t>
+          <t>9,35; 18,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 23,44</t>
+          <t>19,35; 28,62</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,74; 37,4</t>
+          <t>22,17; 36,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,37</t>
+          <t>1,57; 7,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 23,98</t>
+          <t>14,9; 24,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,74; 37,4</t>
+          <t>22,17; 36,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,37</t>
+          <t>1,57; 7,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 23,98</t>
+          <t>14,9; 24,17</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -1035,32 +1035,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,43; 27,6</t>
+          <t>15,53; 26,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,03; 24,16</t>
+          <t>13,3; 23,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,24; 21,6</t>
+          <t>11,79; 21,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,43; 27,6</t>
+          <t>15,53; 26,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,03; 24,16</t>
+          <t>13,3; 23,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,24; 21,6</t>
+          <t>11,79; 21,1</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -1115,32 +1115,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,51; 28,2</t>
+          <t>20,68; 28,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,1; 27,52</t>
+          <t>20,17; 27,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,58; 49,4</t>
+          <t>39,15; 47,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,51; 28,2</t>
+          <t>20,68; 28,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,1; 27,52</t>
+          <t>20,17; 27,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,58; 49,4</t>
+          <t>39,15; 47,83</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -1195,32 +1195,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,06; 26,39</t>
+          <t>18,97; 26,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,65; 17,53</t>
+          <t>11,63; 17,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,22; 14,75</t>
+          <t>9,01; 14,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,06; 26,39</t>
+          <t>18,97; 26,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,65; 17,53</t>
+          <t>11,63; 17,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,22; 14,75</t>
+          <t>9,01; 14,71</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -1275,32 +1275,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21,97; 25,6</t>
+          <t>22,29; 25,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,06; 16,96</t>
+          <t>14,19; 16,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20,01; 25,0</t>
+          <t>22,61; 26,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21,97; 25,6</t>
+          <t>22,29; 25,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,06; 16,96</t>
+          <t>14,19; 16,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,01; 25,0</t>
+          <t>22,61; 26,0</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33720</t>
+          <t>33102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33720</t>
+          <t>33102</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1504,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41826; 69001</t>
+          <t>41037; 68848</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39600; 64124</t>
+          <t>38323; 64642</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25710; 42462</t>
+          <t>25752; 41857</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41826; 69001</t>
+          <t>41037; 68848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39600; 64124</t>
+          <t>38323; 64642</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25710; 42462</t>
+          <t>25752; 41857</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90181</t>
+          <t>94996</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90181</t>
+          <t>94996</t>
         </is>
       </c>
     </row>
@@ -1622,32 +1622,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81457; 118982</t>
+          <t>80113; 116000</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46325; 74109</t>
+          <t>46267; 75734</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76626; 105832</t>
+          <t>80973; 111900</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81457; 118982</t>
+          <t>80113; 116000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46325; 74109</t>
+          <t>46267; 75734</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76626; 105832</t>
+          <t>80973; 111900</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>31085</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>31085</t>
         </is>
       </c>
     </row>
@@ -1740,32 +1740,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44516; 72459</t>
+          <t>44758; 73464</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9661; 25551</t>
+          <t>9175; 24204</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23480; 38981</t>
+          <t>23038; 39316</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44516; 72459</t>
+          <t>44758; 73464</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9661; 25551</t>
+          <t>9175; 24204</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23480; 38981</t>
+          <t>23038; 39316</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52276</t>
+          <t>58299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52276</t>
+          <t>58299</t>
         </is>
       </c>
     </row>
@@ -1858,32 +1858,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72984; 104369</t>
+          <t>72790; 102996</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26729; 50670</t>
+          <t>26672; 51620</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24566; 76512</t>
+          <t>48441; 71654</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72984; 104369</t>
+          <t>72790; 102996</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26729; 50670</t>
+          <t>26672; 51620</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24566; 76512</t>
+          <t>48441; 71654</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>26988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>26988</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>38527; 63361</t>
+          <t>37555; 61562</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2659; 12478</t>
+          <t>2654; 11874</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18848; 30994</t>
+          <t>20836; 33787</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38527; 63361</t>
+          <t>37555; 61562</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2659; 12478</t>
+          <t>2654; 11874</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18848; 30994</t>
+          <t>20836; 33787</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>23207</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>23207</t>
         </is>
       </c>
     </row>
@@ -2094,32 +2094,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33142; 59283</t>
+          <t>33362; 57735</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27003; 50069</t>
+          <t>27563; 48628</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15391; 29575</t>
+          <t>16554; 29634</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33142; 59283</t>
+          <t>33362; 57735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27003; 50069</t>
+          <t>27563; 48628</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15391; 29575</t>
+          <t>16554; 29634</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>170898</t>
+          <t>195796</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>170898</t>
+          <t>195796</t>
         </is>
       </c>
     </row>
@@ -2212,32 +2212,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>114717; 157733</t>
+          <t>115652; 158315</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>108772; 148909</t>
+          <t>109135; 148210</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>153629; 187004</t>
+          <t>176130; 215176</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>114717; 157733</t>
+          <t>115652; 158315</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>108772; 148909</t>
+          <t>109135; 148210</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>153629; 187004</t>
+          <t>176130; 215176</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43286</t>
+          <t>49350</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43286</t>
+          <t>49350</t>
         </is>
       </c>
     </row>
@@ -2330,32 +2330,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>108737; 150557</t>
+          <t>108223; 151443</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>78186; 117650</t>
+          <t>78039; 115486</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>34633; 55403</t>
+          <t>38247; 62430</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>108737; 150557</t>
+          <t>108223; 151443</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>78186; 117650</t>
+          <t>78039; 115486</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34633; 55403</t>
+          <t>38247; 62430</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>467337</t>
+          <t>512824</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>467337</t>
+          <t>512824</t>
         </is>
       </c>
     </row>
@@ -2448,32 +2448,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>601929; 701351</t>
+          <t>610767; 709432</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>390425; 470981</t>
+          <t>393932; 471432</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>403168; 503641</t>
+          <t>477218; 548651</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>601929; 701351</t>
+          <t>610767; 709432</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>390425; 470981</t>
+          <t>393932; 471432</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>403168; 503641</t>
+          <t>477218; 548651</t>
         </is>
       </c>
     </row>
